--- a/2022/Mount1/Mount1_members_final.xlsx
+++ b/2022/Mount1/Mount1_members_final.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
